--- a/preds_oro_fnn.xlsx
+++ b/preds_oro_fnn.xlsx
@@ -417,11 +417,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>horizonte</t>
-        </is>
-      </c>
       <c r="B1" t="inlineStr">
         <is>
           <t>resultados</t>
@@ -430,42 +425,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>101.7767360873029</v>
+        <v>14.99510955810547</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>103.7929563423226</v>
+        <v>51.05453491210938</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>105.7707500397632</v>
+        <v>32.15620040893555</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>107.7122339461439</v>
+        <v>38.42443466186523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109.6193373422939</v>
+        <v>28.34749603271484</v>
       </c>
     </row>
   </sheetData>
